--- a/checklist_forms/050_project_offboarding_checklist--checklist_forms.xlsx
+++ b/checklist_forms/050_project_offboarding_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Page 1</t>
+          <t>Project Goals</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List 1</t>
+          <t>Project Offboarding Checklist Section 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,14 +571,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What was the primary goal of the project?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>What was the primary goal of the project?</t>
-        </is>
-      </c>
+          <t>What was the primary project goal?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_page_2</t>
+          <t>project_offboarding_checklist_field_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist</t>
+          <t>What was the project budget?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_2</t>
+          <t>project_offboarding_checklist_field_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist</t>
+          <t>What were the project deliverables?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_3</t>
+          <t>project_offboarding_checklist_field_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What was the project deliverable?</t>
+          <t>What were the project risks?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_4</t>
+          <t>project_offboarding_checklist_field_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_page_3</t>
+          <t>project_offboarding_checklist_page_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List</t>
+          <t>Project Team</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_3</t>
+          <t>project_offboarding_checklist_section_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List</t>
+          <t>Project Offboarding Checklist Section 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,19 +750,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_5</t>
+          <t>project_offboarding_checklist_field_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What was the project budget?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>What was the project budget?</t>
-        </is>
-      </c>
+          <t>Who was the project manager?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -776,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_6</t>
+          <t>project_offboarding_checklist_field_8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What was the project timeline?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>What was the project timeline?</t>
-        </is>
-      </c>
+          <t>What was the project start date?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -803,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_page_4</t>
+          <t>project_offboarding_checklist_field_9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist</t>
+          <t>What was the project end date?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -826,12 +814,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_4</t>
+          <t>project_offboarding_checklist_page_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -854,19 +842,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_7</t>
+          <t>project_offboarding_checklist_section_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What were the project risks?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>What were the project risks?</t>
-        </is>
-      </c>
+          <t>Project Offboarding Checklist Section 3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -881,19 +865,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_8</t>
+          <t>project_offboarding_checklist_field_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What were the project deliverables?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>What were the project deliverables?</t>
-        </is>
-      </c>
+          <t>What were the project team members?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -903,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_page_5</t>
+          <t>project_offboarding_checklist_field_11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List</t>
+          <t>What were the project dependencies?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -926,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_5</t>
+          <t>project_offboarding_checklist_field_12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List</t>
+          <t>What were the project outcomes?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>project_goal_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Project Goal 1</t>
         </is>
       </c>
     </row>
@@ -1007,250 +987,267 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>project_goal_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Project Goal 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_2_choices</t>
+          <t>project_offboarding_checklist_field_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_1</t>
+          <t>project_deliverable_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist 1</t>
+          <t>Project Deliverable 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_2_choices</t>
+          <t>project_offboarding_checklist_field_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_2</t>
+          <t>project_deliverable_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist 2</t>
+          <t>Project Deliverable 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_2_choices</t>
+          <t>project_offboarding_checklist_field_5_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_3</t>
+          <t>project_risk_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist 3</t>
+          <t>Project Risk 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_3_choices</t>
+          <t>project_offboarding_checklist_field_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_offboarding_check_list_1</t>
+          <t>project_risk_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List 1</t>
+          <t>Project Risk 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_3_choices</t>
+          <t>project_offboarding_checklist_field_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_offboarding_check_list_2</t>
+          <t>project_risk_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List 2</t>
+          <t>Project Risk 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_4_choices</t>
+          <t>project_offboarding_checklist_section_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_1</t>
+          <t>project_team_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist 1</t>
+          <t>Project Team 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_4_choices</t>
+          <t>project_offboarding_checklist_section_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_2</t>
+          <t>project_team_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Project Offboarding Checklist 2</t>
+          <t>Project Team 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_7_choices</t>
+          <t>project_offboarding_checklist_section_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_risk_1</t>
+          <t>project_offboarding_checklist_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Project Risk 1</t>
+          <t>Project Offboarding Checklist 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_7_choices</t>
+          <t>project_offboarding_checklist_section_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>project_risk_2</t>
+          <t>project_offboarding_checklist_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Project Risk 2</t>
+          <t>Project Offboarding Checklist 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_7_choices</t>
+          <t>project_offboarding_checklist_field_10_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_risk_3</t>
+          <t>project_team_member_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Risk 3</t>
+          <t>Project Team Member 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_8_choices</t>
+          <t>project_offboarding_checklist_field_10_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_deliverable_1</t>
+          <t>project_team_member_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Project Deliverable 1</t>
+          <t>Project Team Member 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_field_8_choices</t>
+          <t>project_offboarding_checklist_field_11_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_deliverable_2</t>
+          <t>project_dependency_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Project Deliverable 2</t>
+          <t>Project Dependency 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_5_choices</t>
+          <t>project_offboarding_checklist_field_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_offboarding_check_list_1</t>
+          <t>project_dependency_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List 1</t>
+          <t>Project Dependency 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>project_offboarding_checklist_section_5_choices</t>
+          <t>project_offboarding_checklist_field_12_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_offboarding_check_list_2</t>
+          <t>project_outcome_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Project Offboarding Check List 2</t>
+          <t>Project Outcome 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>project_offboarding_checklist_field_12_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>project_outcome_2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Project Outcome 2</t>
         </is>
       </c>
     </row>
